--- a/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
+++ b/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
@@ -12,7 +12,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+  <si>
+    <t xml:space="preserve">:table Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a damaging effect is made of.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primary index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what it is called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice</t>
+  </si>
   <si>
     <t xml:space="preserve">:table Skill</t>
   </si>
@@ -20,36 +71,9 @@
     <t xml:space="preserve">Skills whose effect is one of several shapes.</t>
   </si>
   <si>
-    <t xml:space="preserve">:field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:target</t>
-  </si>
-  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">primary index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">plain column, outside the group</t>
   </si>
   <si>
@@ -74,10 +98,13 @@
     <t xml:space="preserve">Effect.Pierces</t>
   </si>
   <si>
+    <t xml:space="preserve">Effect.ElementId</t>
+  </si>
+  <si>
     <t xml:space="preserve">Effect.Amount</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
+    <t xml:space="preserve">Effect.Band</t>
   </si>
   <si>
     <t xml:space="preserve">Slash</t>
@@ -95,9 +122,6 @@
     <t xml:space="preserve">TRUE</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mend</t>
   </si>
   <si>
@@ -108,6 +132,9 @@
   </si>
   <si>
     <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -185,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:I11"/>
+  <dimension ref="B2:O11"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -195,6 +222,12 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -206,20 +239,35 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -232,20 +280,35 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -258,20 +321,35 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -284,11 +362,8 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
@@ -297,122 +372,182 @@
         <v>9</v>
       </c>
       <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="s">
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="J10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="J11" t="s">
         <v>38</v>
       </c>
-      <c r="G10" t="s">
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" t="s">
         <v>39</v>
       </c>
-      <c r="H10" t="s">
+      <c r="O11" t="s">
         <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
+++ b/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Polymorphism" sheetId="1" r:id="rId3"/>
+    <sheet name="PolymorphicArray" sheetId="2" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="66">
   <si>
     <t xml:space="preserve">:table Element</t>
   </si>
@@ -168,6 +169,48 @@
   </si>
   <si>
     <t xml:space="preserve">Mend2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Combo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skills whose effects are a list, each element its own shape.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].$type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which shape this element's effect is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].Chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].Pierces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].ElementId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects[].Band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flurry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
   </si>
 </sst>
 </file>
@@ -553,4 +596,324 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:K12"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
+++ b/test/fixtures/xlsx/polymorphism/polymorphism.xlsx
@@ -6,14 +6,114 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Polymorphism" sheetId="1" r:id="rId3"/>
-    <sheet name="PolymorphicArray" sheetId="2" r:id="rId4"/>
+    <sheet name="PolymorphicSubset" sheetId="1" r:id="rId3"/>
+    <sheet name="Polymorphism" sheetId="2" r:id="rId4"/>
+    <sheet name="PolymorphicArray" sheetId="3" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="79">
+  <si>
+    <t xml:space="preserve">:table Boon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blessings whose effect is one of several shapes, written without the columns no row uses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primary index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain column, outside the group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.$type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which shape this row's effect is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Pierces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
   <si>
     <t xml:space="preserve">:table Element</t>
   </si>
@@ -21,48 +121,15 @@
     <t xml:space="preserve">What a damaging effect is made of.</t>
   </si>
   <si>
-    <t xml:space="preserve">:field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:target</t>
-  </si>
-  <si>
     <t xml:space="preserve">code</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">primary index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">what it is called</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fire</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ice</t>
   </si>
   <si>
@@ -72,39 +139,9 @@
     <t xml:space="preserve">Skills whose effect is one of several shapes.</t>
   </si>
   <si>
-    <t xml:space="preserve">index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plain column, outside the group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect.$type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which shape this row's effect is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect.Chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect.Damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect.Pierces</t>
-  </si>
-  <si>
     <t xml:space="preserve">Effect.ElementId</t>
   </si>
   <si>
-    <t xml:space="preserve">Effect.Amount</t>
-  </si>
-  <si>
     <t xml:space="preserve">Effect.Band</t>
   </si>
   <si>
@@ -126,9 +163,6 @@
     <t xml:space="preserve">Mend</t>
   </si>
   <si>
-    <t xml:space="preserve">HealEffect</t>
-  </si>
-  <si>
     <t xml:space="preserve">100</t>
   </si>
   <si>
@@ -138,15 +172,9 @@
     <t xml:space="preserve">Common</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feint</t>
   </si>
   <si>
-    <t xml:space="preserve">NoEffect</t>
-  </si>
-  <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
@@ -165,12 +193,27 @@
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mend2</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Curse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afflictions whose effect is one of several shapes, written without the columns no row uses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wither</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Null</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Combo</t>
   </si>
   <si>
@@ -208,9 +251,6 @@
   </si>
   <si>
     <t xml:space="preserve">Chain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
   </si>
 </sst>
 </file>
@@ -255,7 +295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:O11"/>
+  <dimension ref="B2:I9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -265,12 +305,6 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -282,35 +316,20 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
       <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -323,35 +342,20 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
       <c r="F4" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -364,35 +368,20 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -405,8 +394,11 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
@@ -415,182 +407,76 @@
         <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="G11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -600,15 +486,546 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:X11"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" t="s">
+        <v>17</v>
+      </c>
+      <c r="V4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5" t="s">
+        <v>12</v>
+      </c>
+      <c r="S5" t="s">
+        <v>15</v>
+      </c>
+      <c r="T5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V5" t="s">
+        <v>17</v>
+      </c>
+      <c r="W5" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" t="s">
+        <v>9</v>
+      </c>
+      <c r="U6" t="s">
+        <v>9</v>
+      </c>
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>53</v>
+      </c>
+      <c r="V7" t="s">
+        <v>58</v>
+      </c>
+      <c r="W7" t="s">
+        <v>26</v>
+      </c>
+      <c r="X7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" t="s">
+        <v>17</v>
+      </c>
+      <c r="V8" t="s">
+        <v>17</v>
+      </c>
+      <c r="W8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" t="s">
+        <v>28</v>
+      </c>
+      <c r="T9" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" t="s">
+        <v>17</v>
+      </c>
+      <c r="V9" t="s">
+        <v>17</v>
+      </c>
+      <c r="W9" t="s">
+        <v>17</v>
+      </c>
+      <c r="X9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="B2:K12"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -616,31 +1033,31 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -654,25 +1071,25 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -683,28 +1100,28 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -741,176 +1158,176 @@
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
